--- a/dados.xlsx
+++ b/dados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/botelho/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/botelho/Documents/GitHub/MeuRepositorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61E85787-0C09-FD47-A03B-EA62CDB2A20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D760206-9DF9-7842-B44A-9EA150EA1FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24280" yWindow="12700" windowWidth="28240" windowHeight="17240" xr2:uid="{6D663E8A-5A48-6E48-96CF-99FA06B5C985}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Bairro</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>49a</t>
+  </si>
+  <si>
+    <t>49b</t>
   </si>
 </sst>
 </file>
@@ -457,6 +460,9 @@
       <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B4">

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/botelho/Documents/GitHub/MeuRepositorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D760206-9DF9-7842-B44A-9EA150EA1FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59EE6F87-999F-E742-9733-58CF4601484C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24280" yWindow="12700" windowWidth="28240" windowHeight="17240" xr2:uid="{6D663E8A-5A48-6E48-96CF-99FA06B5C985}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Bairro</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>49b</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -468,6 +471,9 @@
       <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B5">

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/botelho/Documents/GitHub/MeuRepositorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59EE6F87-999F-E742-9733-58CF4601484C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B26FD5-19BC-2846-96FE-EE65071F86C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24280" yWindow="12700" windowWidth="28240" windowHeight="17240" xr2:uid="{6D663E8A-5A48-6E48-96CF-99FA06B5C985}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Bairro</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>49b</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
 </sst>
 </file>
@@ -471,9 +468,6 @@
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B5">
